--- a/artfynd/A 30829-2026 artfynd.xlsx
+++ b/artfynd/A 30829-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1096,10 +1096,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135466834</v>
+        <v>136927977</v>
       </c>
       <c r="B6" t="n">
-        <v>8452</v>
+        <v>58005</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1107,42 +1107,45 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stögölen, Stögölen, Ög</t>
+          <t>Luvebo, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569614</v>
+        <v>569594</v>
       </c>
       <c r="R6" t="n">
-        <v>6511471</v>
+        <v>6511534</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1186,18 +1189,700 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136927977</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136928052</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58005</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Luvebo, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>569613</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6511500</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska födosöksspår i tall låga.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136928052</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136928067</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58005</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Luvebo, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>569616</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6511467</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska födosökspår i liggande död gran</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136928067</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136928213</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58005</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Luvebo, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>569578</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6511549</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska födosökspår i död stående gran</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136928213</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136928343</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58005</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Luvebo, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>569535</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6511657</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska födosökspår i tallraka</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136928343</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135466834</v>
+      </c>
+      <c r="B11" t="n">
+        <v>8452</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stögölen, Stögölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>569614</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6511471</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/135466834</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136928165</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99270</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Luvebo, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>569651</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6511501</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136928165</t>
         </is>
       </c>
     </row>
@@ -1208,6 +1893,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30829-2026 artfynd.xlsx
+++ b/artfynd/A 30829-2026 artfynd.xlsx
@@ -1776,7 +1776,7 @@
         <v>136928165</v>
       </c>
       <c r="B12" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 30829-2026 artfynd.xlsx
+++ b/artfynd/A 30829-2026 artfynd.xlsx
@@ -1776,7 +1776,7 @@
         <v>136928165</v>
       </c>
       <c r="B12" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 30829-2026 artfynd.xlsx
+++ b/artfynd/A 30829-2026 artfynd.xlsx
@@ -1776,7 +1776,7 @@
         <v>136928165</v>
       </c>
       <c r="B12" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 30829-2026 artfynd.xlsx
+++ b/artfynd/A 30829-2026 artfynd.xlsx
@@ -1776,7 +1776,7 @@
         <v>136928165</v>
       </c>
       <c r="B12" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 30829-2026 artfynd.xlsx
+++ b/artfynd/A 30829-2026 artfynd.xlsx
@@ -1776,7 +1776,7 @@
         <v>136928165</v>
       </c>
       <c r="B12" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 30829-2026 artfynd.xlsx
+++ b/artfynd/A 30829-2026 artfynd.xlsx
@@ -1776,7 +1776,7 @@
         <v>136928165</v>
       </c>
       <c r="B12" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 30829-2026 artfynd.xlsx
+++ b/artfynd/A 30829-2026 artfynd.xlsx
@@ -1776,7 +1776,7 @@
         <v>136928165</v>
       </c>
       <c r="B12" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 30829-2026 artfynd.xlsx
+++ b/artfynd/A 30829-2026 artfynd.xlsx
@@ -1099,7 +1099,7 @@
         <v>136927977</v>
       </c>
       <c r="B6" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>136928052</v>
       </c>
       <c r="B7" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>136928067</v>
       </c>
       <c r="B8" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>136928213</v>
       </c>
       <c r="B9" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>136928343</v>
       </c>
       <c r="B10" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>136928165</v>
       </c>
       <c r="B12" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 30829-2026 artfynd.xlsx
+++ b/artfynd/A 30829-2026 artfynd.xlsx
@@ -1099,7 +1099,7 @@
         <v>136927977</v>
       </c>
       <c r="B6" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>136928052</v>
       </c>
       <c r="B7" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>136928067</v>
       </c>
       <c r="B8" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>136928213</v>
       </c>
       <c r="B9" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>136928343</v>
       </c>
       <c r="B10" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>136928165</v>
       </c>
       <c r="B12" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 30829-2026 artfynd.xlsx
+++ b/artfynd/A 30829-2026 artfynd.xlsx
@@ -1127,11 +1127,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1237,11 +1233,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1352,11 +1344,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1467,11 +1455,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1582,11 +1566,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>

--- a/artfynd/A 30829-2026 artfynd.xlsx
+++ b/artfynd/A 30829-2026 artfynd.xlsx
@@ -1756,7 +1756,7 @@
         <v>136928165</v>
       </c>
       <c r="B12" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 30829-2026 artfynd.xlsx
+++ b/artfynd/A 30829-2026 artfynd.xlsx
@@ -1099,7 +1099,7 @@
         <v>136927977</v>
       </c>
       <c r="B6" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>136928052</v>
       </c>
       <c r="B7" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>136928067</v>
       </c>
       <c r="B8" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>136928213</v>
       </c>
       <c r="B9" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>136928343</v>
       </c>
       <c r="B10" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>136928165</v>
       </c>
       <c r="B12" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 30829-2026 artfynd.xlsx
+++ b/artfynd/A 30829-2026 artfynd.xlsx
@@ -1756,7 +1756,7 @@
         <v>136928165</v>
       </c>
       <c r="B12" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 30829-2026 artfynd.xlsx
+++ b/artfynd/A 30829-2026 artfynd.xlsx
@@ -1099,7 +1099,7 @@
         <v>136927977</v>
       </c>
       <c r="B6" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>136928052</v>
       </c>
       <c r="B7" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>136928067</v>
       </c>
       <c r="B8" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>136928213</v>
       </c>
       <c r="B9" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>136928343</v>
       </c>
       <c r="B10" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>136928165</v>
       </c>
       <c r="B12" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 30829-2026 artfynd.xlsx
+++ b/artfynd/A 30829-2026 artfynd.xlsx
@@ -1756,7 +1756,7 @@
         <v>136928165</v>
       </c>
       <c r="B12" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 30829-2026 artfynd.xlsx
+++ b/artfynd/A 30829-2026 artfynd.xlsx
@@ -1099,7 +1099,7 @@
         <v>136927977</v>
       </c>
       <c r="B6" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>136928052</v>
       </c>
       <c r="B7" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>136928067</v>
       </c>
       <c r="B8" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>136928213</v>
       </c>
       <c r="B9" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>136928343</v>
       </c>
       <c r="B10" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>136928165</v>
       </c>
       <c r="B12" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 30829-2026 artfynd.xlsx
+++ b/artfynd/A 30829-2026 artfynd.xlsx
@@ -1756,7 +1756,7 @@
         <v>136928165</v>
       </c>
       <c r="B12" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 30829-2026 artfynd.xlsx
+++ b/artfynd/A 30829-2026 artfynd.xlsx
@@ -1756,7 +1756,7 @@
         <v>136928165</v>
       </c>
       <c r="B12" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 30829-2026 artfynd.xlsx
+++ b/artfynd/A 30829-2026 artfynd.xlsx
@@ -1756,7 +1756,7 @@
         <v>136928165</v>
       </c>
       <c r="B12" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
